--- a/abc.xlsx
+++ b/abc.xlsx
@@ -1174,12 +1174,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/abc.xlsx
+++ b/abc.xlsx
@@ -1174,17 +1174,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="1"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/abc.xlsx
+++ b/abc.xlsx
@@ -1174,12 +1174,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/abc.xlsx
+++ b/abc.xlsx
@@ -1174,8 +1174,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1">
@@ -1192,6 +1192,11 @@
         <v>3</v>
       </c>
     </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/abc.xlsx
+++ b/abc.xlsx
@@ -1174,8 +1174,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1">
@@ -1197,6 +1197,11 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
